--- a/resources/templates/standard/J1100-12.xlsx
+++ b/resources/templates/standard/J1100-12.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="62">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>에스켈레이션(Escalation) 기준서</t>
   </si>
@@ -765,12 +768,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.15" customHeight="1" spans="1:58" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -800,21 +805,21 @@
       <c r="AE1" s="2"/>
       <c r="AF1" s="2"/>
       <c r="AG1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH1" s="3"/>
       <c r="AI1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK1" s="4"/>
       <c r="AL1" s="4"/>
       <c r="AM1" s="4"/>
       <c r="AN1" s="4"/>
       <c r="AO1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP1" s="4"/>
       <c r="AQ1" s="4"/>
@@ -825,17 +830,17 @@
       <c r="AV1" s="4"/>
       <c r="AW1" s="4"/>
       <c r="AX1" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY1" s="4"/>
       <c r="AZ1" s="4"/>
       <c r="BA1" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB1" s="4"/>
       <c r="BC1" s="4"/>
       <c r="BD1" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BE1" s="4"/>
       <c r="BF1" s="4"/>
@@ -966,7 +971,7 @@
     </row>
     <row r="4" ht="20.15" customHeight="1" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -984,7 +989,7 @@
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
@@ -1046,7 +1051,7 @@
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
       <c r="Q5" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R5" s="9"/>
       <c r="S5" s="9"/>
@@ -1108,12 +1113,12 @@
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
       <c r="Q6" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R6" s="12"/>
       <c r="S6" s="12"/>
       <c r="T6" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U6" s="12"/>
       <c r="V6" s="12"/>
@@ -1131,7 +1136,7 @@
       <c r="AH6" s="12"/>
       <c r="AI6" s="12"/>
       <c r="AJ6" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK6" s="12"/>
       <c r="AL6" s="12"/>
@@ -1142,7 +1147,7 @@
       <c r="AQ6" s="12"/>
       <c r="AR6" s="12"/>
       <c r="AS6" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT6" s="13"/>
       <c r="AU6" s="13"/>
@@ -1150,13 +1155,13 @@
       <c r="AW6" s="13"/>
       <c r="AX6" s="13"/>
       <c r="AY6" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ6" s="13"/>
       <c r="BA6" s="13"/>
       <c r="BB6" s="13"/>
       <c r="BC6" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD6" s="13"/>
       <c r="BE6" s="13"/>
@@ -1180,12 +1185,12 @@
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R7" s="14"/>
       <c r="S7" s="14"/>
       <c r="T7" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U7" s="14"/>
       <c r="V7" s="14"/>
@@ -1203,7 +1208,7 @@
       <c r="AH7" s="14"/>
       <c r="AI7" s="14"/>
       <c r="AJ7" s="14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK7" s="14"/>
       <c r="AL7" s="14"/>
@@ -1214,7 +1219,7 @@
       <c r="AQ7" s="14"/>
       <c r="AR7" s="14"/>
       <c r="AS7" s="15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT7" s="15"/>
       <c r="AU7" s="15"/>
@@ -1222,13 +1227,13 @@
       <c r="AW7" s="15"/>
       <c r="AX7" s="15"/>
       <c r="AY7" s="15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ7" s="15"/>
       <c r="BA7" s="15"/>
       <c r="BB7" s="15"/>
       <c r="BC7" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD7" s="15"/>
       <c r="BE7" s="15"/>
@@ -1252,12 +1257,12 @@
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
       <c r="Q8" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
       <c r="T8" s="14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
@@ -1275,7 +1280,7 @@
       <c r="AH8" s="14"/>
       <c r="AI8" s="14"/>
       <c r="AJ8" s="14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK8" s="14"/>
       <c r="AL8" s="14"/>
@@ -1318,12 +1323,12 @@
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R9" s="16"/>
       <c r="S9" s="16"/>
       <c r="T9" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="U9" s="14"/>
       <c r="V9" s="14"/>
@@ -1341,7 +1346,7 @@
       <c r="AH9" s="14"/>
       <c r="AI9" s="14"/>
       <c r="AJ9" s="14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK9" s="14"/>
       <c r="AL9" s="14"/>
@@ -1384,12 +1389,12 @@
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
       <c r="Q10" s="17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R10" s="17"/>
       <c r="S10" s="17"/>
       <c r="T10" s="17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="U10" s="17"/>
       <c r="V10" s="17"/>
@@ -1407,7 +1412,7 @@
       <c r="AH10" s="17"/>
       <c r="AI10" s="17"/>
       <c r="AJ10" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AK10" s="14"/>
       <c r="AL10" s="14"/>
@@ -1450,7 +1455,7 @@
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
       <c r="Q11" s="18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R11" s="18"/>
       <c r="S11" s="18"/>
@@ -1512,12 +1517,12 @@
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
       <c r="Q12" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U12" s="12"/>
       <c r="V12" s="12"/>
@@ -1535,7 +1540,7 @@
       <c r="AH12" s="12"/>
       <c r="AI12" s="12"/>
       <c r="AJ12" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK12" s="12"/>
       <c r="AL12" s="12"/>
@@ -1546,7 +1551,7 @@
       <c r="AQ12" s="12"/>
       <c r="AR12" s="12"/>
       <c r="AS12" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT12" s="13"/>
       <c r="AU12" s="13"/>
@@ -1554,13 +1559,13 @@
       <c r="AW12" s="13"/>
       <c r="AX12" s="13"/>
       <c r="AY12" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ12" s="13"/>
       <c r="BA12" s="13"/>
       <c r="BB12" s="13"/>
       <c r="BC12" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD12" s="13"/>
       <c r="BE12" s="13"/>
@@ -1584,12 +1589,12 @@
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
       <c r="Q13" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R13" s="14"/>
       <c r="S13" s="14"/>
       <c r="T13" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U13" s="14"/>
       <c r="V13" s="14"/>
@@ -1607,7 +1612,7 @@
       <c r="AH13" s="14"/>
       <c r="AI13" s="14"/>
       <c r="AJ13" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AK13" s="14"/>
       <c r="AL13" s="14"/>
@@ -1618,7 +1623,7 @@
       <c r="AQ13" s="14"/>
       <c r="AR13" s="14"/>
       <c r="AS13" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AT13" s="15"/>
       <c r="AU13" s="15"/>
@@ -1626,13 +1631,13 @@
       <c r="AW13" s="15"/>
       <c r="AX13" s="15"/>
       <c r="AY13" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AZ13" s="15"/>
       <c r="BA13" s="15"/>
       <c r="BB13" s="15"/>
       <c r="BC13" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BD13" s="15"/>
       <c r="BE13" s="15"/>
@@ -1656,12 +1661,12 @@
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
       <c r="Q14" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R14" s="14"/>
       <c r="S14" s="14"/>
       <c r="T14" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U14" s="14"/>
       <c r="V14" s="14"/>
@@ -1679,7 +1684,7 @@
       <c r="AH14" s="14"/>
       <c r="AI14" s="14"/>
       <c r="AJ14" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AK14" s="14"/>
       <c r="AL14" s="14"/>
@@ -1722,12 +1727,12 @@
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R15" s="16"/>
       <c r="S15" s="16"/>
       <c r="T15" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U15" s="14"/>
       <c r="V15" s="14"/>
@@ -1745,7 +1750,7 @@
       <c r="AH15" s="14"/>
       <c r="AI15" s="14"/>
       <c r="AJ15" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AK15" s="14"/>
       <c r="AL15" s="14"/>
@@ -1788,12 +1793,12 @@
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
       <c r="Q16" s="17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R16" s="17"/>
       <c r="S16" s="17"/>
       <c r="T16" s="17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U16" s="17"/>
       <c r="V16" s="17"/>
@@ -1811,7 +1816,7 @@
       <c r="AH16" s="17"/>
       <c r="AI16" s="17"/>
       <c r="AJ16" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AK16" s="14"/>
       <c r="AL16" s="14"/>
@@ -1854,7 +1859,7 @@
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
       <c r="Q17" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R17" s="18"/>
       <c r="S17" s="18"/>
@@ -1916,12 +1921,12 @@
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
       <c r="Q18" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R18" s="12"/>
       <c r="S18" s="12"/>
       <c r="T18" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U18" s="12"/>
       <c r="V18" s="12"/>
@@ -1939,7 +1944,7 @@
       <c r="AH18" s="12"/>
       <c r="AI18" s="12"/>
       <c r="AJ18" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK18" s="12"/>
       <c r="AL18" s="12"/>
@@ -1950,7 +1955,7 @@
       <c r="AQ18" s="12"/>
       <c r="AR18" s="12"/>
       <c r="AS18" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT18" s="13"/>
       <c r="AU18" s="13"/>
@@ -1958,13 +1963,13 @@
       <c r="AW18" s="13"/>
       <c r="AX18" s="13"/>
       <c r="AY18" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ18" s="13"/>
       <c r="BA18" s="13"/>
       <c r="BB18" s="13"/>
       <c r="BC18" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD18" s="13"/>
       <c r="BE18" s="13"/>
@@ -1988,12 +1993,12 @@
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
       <c r="Q19" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R19" s="14"/>
       <c r="S19" s="14"/>
       <c r="T19" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="U19" s="14"/>
       <c r="V19" s="14"/>
@@ -2011,7 +2016,7 @@
       <c r="AH19" s="14"/>
       <c r="AI19" s="14"/>
       <c r="AJ19" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AK19" s="14"/>
       <c r="AL19" s="14"/>
@@ -2022,7 +2027,7 @@
       <c r="AQ19" s="14"/>
       <c r="AR19" s="14"/>
       <c r="AS19" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AT19" s="15"/>
       <c r="AU19" s="15"/>
@@ -2030,13 +2035,13 @@
       <c r="AW19" s="15"/>
       <c r="AX19" s="15"/>
       <c r="AY19" s="15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AZ19" s="15"/>
       <c r="BA19" s="15"/>
       <c r="BB19" s="15"/>
       <c r="BC19" s="15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="BD19" s="15"/>
       <c r="BE19" s="15"/>
@@ -2060,12 +2065,12 @@
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
       <c r="Q20" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R20" s="14"/>
       <c r="S20" s="14"/>
       <c r="T20" s="14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U20" s="14"/>
       <c r="V20" s="14"/>
@@ -2083,7 +2088,7 @@
       <c r="AH20" s="14"/>
       <c r="AI20" s="14"/>
       <c r="AJ20" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AK20" s="14"/>
       <c r="AL20" s="14"/>
@@ -2126,12 +2131,12 @@
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
       <c r="Q21" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R21" s="16"/>
       <c r="S21" s="16"/>
       <c r="T21" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U21" s="14"/>
       <c r="V21" s="14"/>
@@ -2149,7 +2154,7 @@
       <c r="AH21" s="14"/>
       <c r="AI21" s="14"/>
       <c r="AJ21" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AK21" s="14"/>
       <c r="AL21" s="14"/>
@@ -2192,12 +2197,12 @@
       <c r="O22" s="8"/>
       <c r="P22" s="8"/>
       <c r="Q22" s="17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R22" s="17"/>
       <c r="S22" s="17"/>
       <c r="T22" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="U22" s="17"/>
       <c r="V22" s="17"/>
@@ -2215,7 +2220,7 @@
       <c r="AH22" s="17"/>
       <c r="AI22" s="17"/>
       <c r="AJ22" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AK22" s="14"/>
       <c r="AL22" s="14"/>
@@ -2258,7 +2263,7 @@
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
       <c r="Q23" s="18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R23" s="18"/>
       <c r="S23" s="18"/>
@@ -2320,7 +2325,7 @@
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
       <c r="Q24" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R24" s="12"/>
       <c r="S24" s="12"/>
@@ -2350,7 +2355,7 @@
       <c r="AQ24" s="12"/>
       <c r="AR24" s="12"/>
       <c r="AS24" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT24" s="13"/>
       <c r="AU24" s="13"/>
@@ -2358,13 +2363,13 @@
       <c r="AW24" s="13"/>
       <c r="AX24" s="13"/>
       <c r="AY24" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ24" s="13"/>
       <c r="BA24" s="13"/>
       <c r="BB24" s="13"/>
       <c r="BC24" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD24" s="13"/>
       <c r="BE24" s="13"/>
@@ -2388,7 +2393,7 @@
       <c r="O25" s="8"/>
       <c r="P25" s="8"/>
       <c r="Q25" s="15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R25" s="15"/>
       <c r="S25" s="15"/>
@@ -2418,7 +2423,7 @@
       <c r="AQ25" s="15"/>
       <c r="AR25" s="15"/>
       <c r="AS25" s="15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AT25" s="15"/>
       <c r="AU25" s="15"/>
@@ -2426,13 +2431,13 @@
       <c r="AW25" s="15"/>
       <c r="AX25" s="15"/>
       <c r="AY25" s="15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AZ25" s="15"/>
       <c r="BA25" s="15"/>
       <c r="BB25" s="15"/>
       <c r="BC25" s="19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="BD25" s="19"/>
       <c r="BE25" s="19"/>
